--- a/各指数夏普比率比较.xlsx
+++ b/各指数夏普比率比较.xlsx
@@ -4,16 +4,17 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20752" windowHeight="9555" tabRatio="918" firstSheet="2" activeTab="3"/>
+    <workbookView windowWidth="20752" windowHeight="9555" tabRatio="918" firstSheet="2" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="宽基系列" sheetId="1" r:id="rId1"/>
-    <sheet name="科创板系列" sheetId="6" r:id="rId2"/>
-    <sheet name="A系列" sheetId="2" r:id="rId3"/>
-    <sheet name="行业系列" sheetId="7" r:id="rId4"/>
-    <sheet name="红利系列" sheetId="3" r:id="rId5"/>
-    <sheet name="红利低波系列" sheetId="4" r:id="rId6"/>
-    <sheet name="现金流系列" sheetId="5" r:id="rId7"/>
+    <sheet name="A系列" sheetId="2" r:id="rId2"/>
+    <sheet name="科创板系列" sheetId="6" r:id="rId3"/>
+    <sheet name="创业板系列" sheetId="8" r:id="rId4"/>
+    <sheet name="行业系列" sheetId="7" r:id="rId5"/>
+    <sheet name="现金流系列" sheetId="5" r:id="rId6"/>
+    <sheet name="红利系列" sheetId="3" r:id="rId7"/>
+    <sheet name="红利低波系列" sheetId="4" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="54">
   <si>
     <t>年份</t>
   </si>
@@ -59,6 +60,21 @@
     <t>平均值</t>
   </si>
   <si>
+    <t>2014-2025平均值</t>
+  </si>
+  <si>
+    <t>中证A50</t>
+  </si>
+  <si>
+    <t>中证A100</t>
+  </si>
+  <si>
+    <t>中证A500</t>
+  </si>
+  <si>
+    <t>2006-2025年平均值</t>
+  </si>
+  <si>
     <t>科创50</t>
   </si>
   <si>
@@ -71,13 +87,22 @@
     <t>科创综指</t>
   </si>
   <si>
-    <t>中证A50</t>
-  </si>
-  <si>
-    <t>中证A100</t>
-  </si>
-  <si>
-    <t>中证A500</t>
+    <t>2023-2025年平均值</t>
+  </si>
+  <si>
+    <t>创业板50</t>
+  </si>
+  <si>
+    <t>创业板指</t>
+  </si>
+  <si>
+    <t>创业200</t>
+  </si>
+  <si>
+    <t>创业板综</t>
+  </si>
+  <si>
+    <t>2013-2025年平均值</t>
   </si>
   <si>
     <t>800能源</t>
@@ -116,15 +141,42 @@
     <t>--</t>
   </si>
   <si>
+    <t>中证现金流</t>
+  </si>
+  <si>
+    <t>300现金流</t>
+  </si>
+  <si>
+    <t>500现金流</t>
+  </si>
+  <si>
+    <t>1000现金流</t>
+  </si>
+  <si>
+    <t>A500现金流</t>
+  </si>
+  <si>
     <t>中证红利</t>
   </si>
   <si>
     <t>红利200</t>
   </si>
   <si>
+    <t>300红利</t>
+  </si>
+  <si>
+    <t>500红利</t>
+  </si>
+  <si>
+    <t>1000红利</t>
+  </si>
+  <si>
     <t>A500红利</t>
   </si>
   <si>
+    <t>全部年份平均值</t>
+  </si>
+  <si>
     <t>红利低波</t>
   </si>
   <si>
@@ -143,19 +195,7 @@
     <t>A500红利低波</t>
   </si>
   <si>
-    <t>中证现金流</t>
-  </si>
-  <si>
-    <t>300现金流</t>
-  </si>
-  <si>
-    <t>500现金流</t>
-  </si>
-  <si>
-    <t>1000现金流</t>
-  </si>
-  <si>
-    <t>A500现金流</t>
+    <t>2014-2025年平均值</t>
   </si>
 </sst>
 </file>
@@ -186,13 +226,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -792,7 +832,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -808,26 +848,44 @@
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1140,10 +1198,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
+    <col min="1" max="1" width="17.1327433628319" style="1" customWidth="1"/>
     <col min="2" max="4" width="12.7964601769912" style="3"/>
     <col min="5" max="5" width="9" style="1"/>
   </cols>
@@ -1178,7 +1236,7 @@
       <c r="A3" s="1">
         <v>2005</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="7">
         <v>-0.515</v>
       </c>
       <c r="C3" s="3">
@@ -1196,7 +1254,7 @@
       <c r="A4" s="1">
         <v>2006</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="7">
         <v>5.414</v>
       </c>
       <c r="C4" s="3">
@@ -1220,7 +1278,7 @@
       <c r="C5" s="3">
         <v>4.41</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="7">
         <v>4.981</v>
       </c>
       <c r="F5">
@@ -1238,7 +1296,7 @@
       <c r="C6" s="3">
         <v>-1.17</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="7">
         <v>-1.141</v>
       </c>
       <c r="F6">
@@ -1256,7 +1314,7 @@
       <c r="C7" s="3">
         <v>3.629</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="7">
         <v>3.848</v>
       </c>
       <c r="F7">
@@ -1274,7 +1332,7 @@
       <c r="C8" s="3">
         <v>0.249</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="7">
         <v>0.501</v>
       </c>
       <c r="F8">
@@ -1286,7 +1344,7 @@
       <c r="A9" s="1">
         <v>2011</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="7">
         <v>-1.379</v>
       </c>
       <c r="C9" s="3">
@@ -1304,7 +1362,7 @@
       <c r="A10" s="1">
         <v>2012</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="7">
         <v>0.229</v>
       </c>
       <c r="C10" s="3">
@@ -1328,7 +1386,7 @@
       <c r="C11" s="3">
         <v>0.617</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="7">
         <v>1.22</v>
       </c>
       <c r="F11">
@@ -1340,7 +1398,7 @@
       <c r="A12" s="1">
         <v>2014</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="7">
         <v>2.568</v>
       </c>
       <c r="C12" s="3">
@@ -1403,7 +1461,7 @@
       <c r="A15" s="1">
         <v>2017</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="7">
         <v>1.884</v>
       </c>
       <c r="C15" s="3">
@@ -1424,7 +1482,7 @@
       <c r="A16" s="1">
         <v>2018</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="7">
         <v>-1.343</v>
       </c>
       <c r="C16" s="3">
@@ -1445,7 +1503,7 @@
       <c r="A17" s="1">
         <v>2019</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="7">
         <v>1.698</v>
       </c>
       <c r="C17" s="3">
@@ -1466,7 +1524,7 @@
       <c r="A18" s="1">
         <v>2020</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="7">
         <v>1.076</v>
       </c>
       <c r="C18" s="3">
@@ -1550,7 +1608,7 @@
       <c r="A22" s="1">
         <v>2024</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="7">
         <v>0.562</v>
       </c>
       <c r="C22" s="3">
@@ -1574,7 +1632,7 @@
       <c r="B23" s="3">
         <v>0.989</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="7">
         <v>1.39</v>
       </c>
       <c r="D23" s="3">
@@ -1592,7 +1650,7 @@
       <c r="A25" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="7">
         <f>SUM(B3:B23)/21</f>
         <v>0.596380952380952</v>
       </c>
@@ -1603,6 +1661,27 @@
       <c r="D25" s="3">
         <f>SUM(D3:D23)/21</f>
         <v>0.551571428571429</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="3">
+        <f>SUM(B12:B23)/12</f>
+        <v>0.338083333333333</v>
+      </c>
+      <c r="C27" s="3">
+        <f>SUM(C12:C23)/12</f>
+        <v>0.2025</v>
+      </c>
+      <c r="D27" s="3">
+        <f>SUM(D12:D23)/12</f>
+        <v>0.115666666666667</v>
+      </c>
+      <c r="E27" s="4">
+        <f>SUM(E12:E23)/12</f>
+        <v>0.371166666666667</v>
       </c>
     </row>
   </sheetData>
@@ -1620,196 +1699,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelCol="5"/>
-  <cols>
-    <col min="2" max="2" width="9.02654867256637" style="9"/>
-    <col min="3" max="3" width="12.7964601769912" style="9"/>
-    <col min="5" max="5" width="9.02654867256637" style="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="1"/>
-      <c r="B2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="1"/>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>2020</v>
-      </c>
-      <c r="B3" s="9">
-        <v>0.826</v>
-      </c>
-      <c r="C3" s="9">
-        <v>0.681</v>
-      </c>
-      <c r="E3" s="10">
-        <v>0.926</v>
-      </c>
-      <c r="F3">
-        <f t="shared" ref="F3:F8" si="0">MAX(B3:E3)</f>
-        <v>0.926</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>2021</v>
-      </c>
-      <c r="B4" s="9">
-        <v>-0.109</v>
-      </c>
-      <c r="C4" s="10">
-        <v>1.066</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.335</v>
-      </c>
-      <c r="F4">
-        <f t="shared" si="0"/>
-        <v>1.066</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>2022</v>
-      </c>
-      <c r="B5" s="9">
-        <v>-1.282</v>
-      </c>
-      <c r="C5" s="9">
-        <v>-1.086</v>
-      </c>
-      <c r="E5" s="10">
-        <v>-1.073</v>
-      </c>
-      <c r="F5">
-        <f t="shared" si="0"/>
-        <v>-1.073</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>2023</v>
-      </c>
-      <c r="B6" s="9">
-        <v>-0.72</v>
-      </c>
-      <c r="C6" s="9">
-        <v>-0.801</v>
-      </c>
-      <c r="D6" s="11">
-        <v>-0.36</v>
-      </c>
-      <c r="E6" s="9">
-        <v>-0.573</v>
-      </c>
-      <c r="F6">
-        <f t="shared" si="0"/>
-        <v>-0.36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>2024</v>
-      </c>
-      <c r="B7" s="9">
-        <v>0.342</v>
-      </c>
-      <c r="C7" s="9">
-        <v>-0.273</v>
-      </c>
-      <c r="D7" s="11">
-        <v>-0.342</v>
-      </c>
-      <c r="E7" s="9">
-        <v>-0.045</v>
-      </c>
-      <c r="F7">
-        <f t="shared" si="0"/>
-        <v>0.342</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>2025</v>
-      </c>
-      <c r="B8" s="9">
-        <v>1.132</v>
-      </c>
-      <c r="C8" s="10">
-        <v>1.753</v>
-      </c>
-      <c r="D8">
-        <v>1.748</v>
-      </c>
-      <c r="E8" s="9">
-        <v>1.553</v>
-      </c>
-      <c r="F8">
-        <f t="shared" si="0"/>
-        <v>1.753</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="9">
-        <f>SUM(B3:B8)/6</f>
-        <v>0.0315</v>
-      </c>
-      <c r="C10" s="9">
-        <f>SUM(C3:C8)/6</f>
-        <v>0.223333333333333</v>
-      </c>
-      <c r="E10" s="10">
-        <f>SUM(B3:B8)/6</f>
-        <v>0.0315</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="F1:F2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
+    <col min="1" max="1" width="20.4513274336283" style="1" customWidth="1"/>
     <col min="2" max="4" width="12.7964601769912" style="3"/>
   </cols>
   <sheetData>
@@ -1826,13 +1719,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="B2" s="3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E2" s="1"/>
     </row>
@@ -1840,8 +1733,8 @@
       <c r="A3" s="1">
         <v>2005</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="D3" s="4">
+      <c r="B3" s="7"/>
+      <c r="D3" s="7">
         <v>-0.606</v>
       </c>
       <c r="E3">
@@ -1853,8 +1746,8 @@
       <c r="A4" s="1">
         <v>2006</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4">
+      <c r="B4" s="7"/>
+      <c r="C4" s="7">
         <v>5.794</v>
       </c>
       <c r="D4" s="3">
@@ -1872,7 +1765,7 @@
       <c r="C5" s="3">
         <v>3.974</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="7">
         <v>4.41</v>
       </c>
       <c r="E5">
@@ -1887,7 +1780,7 @@
       <c r="C6" s="3">
         <v>-1.458</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="7">
         <v>-1.412</v>
       </c>
       <c r="E6">
@@ -1902,7 +1795,7 @@
       <c r="C7" s="3">
         <v>2.659</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="7">
         <v>2.998</v>
       </c>
       <c r="E7">
@@ -1917,7 +1810,7 @@
       <c r="C8" s="3">
         <v>-0.901</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="7">
         <v>-0.446</v>
       </c>
       <c r="E8">
@@ -1929,8 +1822,8 @@
       <c r="A9" s="1">
         <v>2011</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4">
+      <c r="B9" s="7"/>
+      <c r="C9" s="7">
         <v>-1.21</v>
       </c>
       <c r="D9" s="3">
@@ -1945,8 +1838,8 @@
       <c r="A10" s="1">
         <v>2012</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
         <v>0.41</v>
       </c>
       <c r="D10" s="3">
@@ -1964,7 +1857,7 @@
       <c r="C11" s="3">
         <v>-0.714</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="7">
         <v>-0.148</v>
       </c>
       <c r="E11">
@@ -1976,8 +1869,8 @@
       <c r="A12" s="1">
         <v>2014</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4">
+      <c r="B12" s="7"/>
+      <c r="C12" s="7">
         <v>2.73</v>
       </c>
       <c r="D12" s="3">
@@ -1992,13 +1885,13 @@
       <c r="A13" s="1">
         <v>2015</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="16">
         <v>0.037</v>
       </c>
       <c r="C13" s="3">
         <v>-0.116</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="7">
         <v>0.331</v>
       </c>
       <c r="E13">
@@ -2010,7 +1903,7 @@
       <c r="A14" s="1">
         <v>2016</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="17">
         <v>-0.46</v>
       </c>
       <c r="C14" s="3">
@@ -2028,7 +1921,7 @@
       <c r="A15" s="1">
         <v>2017</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="17">
         <v>3.412</v>
       </c>
       <c r="C15" s="3">
@@ -2046,7 +1939,7 @@
       <c r="A16" s="1">
         <v>2018</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="17">
         <v>-1.143</v>
       </c>
       <c r="C16" s="3">
@@ -2064,7 +1957,7 @@
       <c r="A17" s="1">
         <v>2019</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="17">
         <v>2.084</v>
       </c>
       <c r="C17" s="3">
@@ -2082,7 +1975,7 @@
       <c r="A18" s="1">
         <v>2020</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="17">
         <v>1.364</v>
       </c>
       <c r="C18" s="3">
@@ -2100,13 +1993,13 @@
       <c r="A19" s="1">
         <v>2021</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="16">
         <v>-0.404</v>
       </c>
       <c r="C19" s="3">
         <v>-0.699</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="7">
         <v>-0.132</v>
       </c>
       <c r="E19">
@@ -2118,7 +2011,7 @@
       <c r="A20" s="1">
         <v>2022</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="17">
         <v>-1.09</v>
       </c>
       <c r="C20" s="3">
@@ -2136,13 +2029,13 @@
       <c r="A21" s="1">
         <v>2023</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="16">
         <v>-1.093</v>
       </c>
       <c r="C21" s="3">
         <v>-1.12</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="7">
         <v>-1.087</v>
       </c>
       <c r="E21">
@@ -2154,7 +2047,7 @@
       <c r="A22" s="1">
         <v>2024</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="17">
         <v>0.595</v>
       </c>
       <c r="C22" s="3">
@@ -2172,13 +2065,13 @@
       <c r="A23" s="1">
         <v>2025</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23" s="16">
         <v>0.745</v>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="6">
         <v>1.131</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="7">
         <v>1.193</v>
       </c>
       <c r="E23">
@@ -2190,7 +2083,7 @@
       <c r="A25" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="7">
         <f>SUM(B13:B23)/11</f>
         <v>0.367909090909091</v>
       </c>
@@ -2201,6 +2094,19 @@
       <c r="D25" s="3">
         <f>SUM(D13:D23)/11</f>
         <v>0.182545454545455</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="3">
+        <f>SUM(C4:C23)/20</f>
+        <v>0.66295</v>
+      </c>
+      <c r="D26" s="4">
+        <f>SUM(D4:D23)/20</f>
+        <v>0.68375</v>
       </c>
     </row>
   </sheetData>
@@ -2215,13 +2121,624 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="20.5132743362832" customWidth="1"/>
+    <col min="2" max="2" width="9.02654867256637" style="12"/>
+    <col min="3" max="3" width="12.7964601769912" style="12"/>
+    <col min="5" max="5" width="9.02654867256637" style="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1"/>
+      <c r="B2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>2020</v>
+      </c>
+      <c r="B3" s="12">
+        <v>0.826</v>
+      </c>
+      <c r="C3" s="12">
+        <v>0.681</v>
+      </c>
+      <c r="E3" s="13">
+        <v>0.926</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F8" si="0">MAX(B3:E3)</f>
+        <v>0.926</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>2021</v>
+      </c>
+      <c r="B4" s="12">
+        <v>-0.109</v>
+      </c>
+      <c r="C4" s="13">
+        <v>1.066</v>
+      </c>
+      <c r="E4" s="12">
+        <v>0.335</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>1.066</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>2022</v>
+      </c>
+      <c r="B5" s="12">
+        <v>-1.282</v>
+      </c>
+      <c r="C5" s="12">
+        <v>-1.086</v>
+      </c>
+      <c r="E5" s="13">
+        <v>-1.073</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>-1.073</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>2023</v>
+      </c>
+      <c r="B6" s="12">
+        <v>-0.72</v>
+      </c>
+      <c r="C6" s="12">
+        <v>-0.801</v>
+      </c>
+      <c r="D6" s="14">
+        <v>-0.36</v>
+      </c>
+      <c r="E6" s="12">
+        <v>-0.573</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>2024</v>
+      </c>
+      <c r="B7" s="12">
+        <v>0.342</v>
+      </c>
+      <c r="C7" s="12">
+        <v>-0.273</v>
+      </c>
+      <c r="D7" s="14">
+        <v>-0.342</v>
+      </c>
+      <c r="E7" s="12">
+        <v>-0.045</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>0.342</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>2025</v>
+      </c>
+      <c r="B8" s="12">
+        <v>1.132</v>
+      </c>
+      <c r="C8" s="13">
+        <v>1.753</v>
+      </c>
+      <c r="D8">
+        <v>1.748</v>
+      </c>
+      <c r="E8" s="12">
+        <v>1.553</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>1.753</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="12">
+        <f>SUM(B3:B8)/6</f>
+        <v>0.0315</v>
+      </c>
+      <c r="C10" s="12">
+        <f>SUM(C3:C8)/6</f>
+        <v>0.223333333333333</v>
+      </c>
+      <c r="E10" s="13">
+        <f>SUM(B3:B8)/6</f>
+        <v>0.0315</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="12">
+        <f>SUM(B6:B8)/3</f>
+        <v>0.251333333333333</v>
+      </c>
+      <c r="C11" s="12">
+        <f>SUM(C6:C8)/3</f>
+        <v>0.226333333333333</v>
+      </c>
+      <c r="D11" s="15">
+        <f>SUM(D6:D8)/3</f>
+        <v>0.348666666666667</v>
+      </c>
+      <c r="E11" s="12">
+        <f>SUM(E6:E8)/3</f>
+        <v>0.311666666666667</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="F1:F2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="20.1858407079646" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.02654867256637" style="3"/>
+    <col min="3" max="3" width="12.7964601769912" style="3"/>
+    <col min="4" max="4" width="9.02654867256637" style="1"/>
+    <col min="5" max="5" width="9.02654867256637" style="3"/>
+    <col min="6" max="6" width="9.02654867256637" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="B2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" spans="1:6">
+      <c r="A3" s="1">
+        <v>2011</v>
+      </c>
+      <c r="B3" s="8">
+        <v>-1.374</v>
+      </c>
+      <c r="C3" s="3">
+        <v>-1.412</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="3">
+        <v>-1.403</v>
+      </c>
+      <c r="F3" s="1">
+        <f>MAX(B3:E3)</f>
+        <v>-1.374</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" spans="1:6">
+      <c r="A4" s="1">
+        <v>2012</v>
+      </c>
+      <c r="B4" s="9">
+        <v>-0.359</v>
+      </c>
+      <c r="C4" s="3">
+        <v>-0.183</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="4">
+        <v>-0.17</v>
+      </c>
+      <c r="F4" s="1">
+        <f t="shared" ref="F4:F17" si="0">MAX(B4:E4)</f>
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" spans="1:6">
+      <c r="A5" s="1">
+        <v>2013</v>
+      </c>
+      <c r="B5" s="8">
+        <v>2.746</v>
+      </c>
+      <c r="C5" s="3">
+        <v>2.513</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1.786</v>
+      </c>
+      <c r="E5" s="3">
+        <v>2.298</v>
+      </c>
+      <c r="F5" s="1">
+        <f t="shared" si="0"/>
+        <v>2.746</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" spans="1:6">
+      <c r="A6" s="1">
+        <v>2014</v>
+      </c>
+      <c r="B6" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.391</v>
+      </c>
+      <c r="D6" s="10">
+        <v>1.473</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0.947</v>
+      </c>
+      <c r="F6" s="1">
+        <f t="shared" si="0"/>
+        <v>1.473</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" spans="1:6">
+      <c r="A7" s="1">
+        <v>2015</v>
+      </c>
+      <c r="B7" s="9">
+        <v>1.525</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1.595</v>
+      </c>
+      <c r="D7" s="10">
+        <v>2.61</v>
+      </c>
+      <c r="E7" s="3">
+        <v>2.099</v>
+      </c>
+      <c r="F7" s="1">
+        <f t="shared" si="0"/>
+        <v>2.61</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" spans="1:6">
+      <c r="A8" s="1">
+        <v>2016</v>
+      </c>
+      <c r="B8" s="9">
+        <v>-1.011</v>
+      </c>
+      <c r="C8" s="3">
+        <v>-0.92</v>
+      </c>
+      <c r="D8" s="1">
+        <v>-0.702</v>
+      </c>
+      <c r="E8" s="4">
+        <v>-0.678</v>
+      </c>
+      <c r="F8" s="1">
+        <f t="shared" si="0"/>
+        <v>-0.678</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" spans="1:6">
+      <c r="A9" s="1">
+        <v>2017</v>
+      </c>
+      <c r="B9" s="9">
+        <v>-0.914</v>
+      </c>
+      <c r="C9" s="4">
+        <v>-0.822</v>
+      </c>
+      <c r="D9" s="1">
+        <v>-1.237</v>
+      </c>
+      <c r="E9" s="3">
+        <v>-1.003</v>
+      </c>
+      <c r="F9" s="1">
+        <f t="shared" si="0"/>
+        <v>-0.822</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" spans="1:6">
+      <c r="A10" s="1">
+        <v>2018</v>
+      </c>
+      <c r="B10" s="9">
+        <v>-1.169</v>
+      </c>
+      <c r="C10" s="4">
+        <v>-1.128</v>
+      </c>
+      <c r="D10" s="1">
+        <v>-1.292</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-1.213</v>
+      </c>
+      <c r="F10" s="1">
+        <f t="shared" si="0"/>
+        <v>-1.128</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" spans="1:6">
+      <c r="A11" s="1">
+        <v>2019</v>
+      </c>
+      <c r="B11" s="8">
+        <v>1.745</v>
+      </c>
+      <c r="C11" s="3">
+        <v>1.565</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1.021</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1.345</v>
+      </c>
+      <c r="F11" s="1">
+        <f t="shared" si="0"/>
+        <v>1.745</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" spans="1:6">
+      <c r="A12" s="1">
+        <v>2020</v>
+      </c>
+      <c r="B12" s="8">
+        <v>2.567</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1.981</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0.415</v>
+      </c>
+      <c r="E12" s="6">
+        <v>1.447</v>
+      </c>
+      <c r="F12" s="1">
+        <f t="shared" si="0"/>
+        <v>2.567</v>
+      </c>
+    </row>
+    <row r="13" customFormat="1" spans="1:6">
+      <c r="A13" s="1">
+        <v>2021</v>
+      </c>
+      <c r="B13" s="9">
+        <v>0.45</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.327</v>
+      </c>
+      <c r="D13" s="10">
+        <v>1.077</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0.658</v>
+      </c>
+      <c r="F13" s="1">
+        <f t="shared" si="0"/>
+        <v>1.077</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" spans="1:6">
+      <c r="A14" s="1">
+        <v>2022</v>
+      </c>
+      <c r="B14" s="9">
+        <v>-1.071</v>
+      </c>
+      <c r="C14" s="3">
+        <v>-1.15</v>
+      </c>
+      <c r="D14" s="10">
+        <v>-0.985</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-1.112</v>
+      </c>
+      <c r="F14" s="1">
+        <f t="shared" si="0"/>
+        <v>-0.985</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="1">
+        <v>2023</v>
+      </c>
+      <c r="B15" s="9">
+        <v>-1.364</v>
+      </c>
+      <c r="C15" s="3">
+        <v>-1.263</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0.114</v>
+      </c>
+      <c r="E15" s="3">
+        <v>-0.499</v>
+      </c>
+      <c r="F15" s="1">
+        <f t="shared" si="0"/>
+        <v>0.114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="1">
+        <v>2024</v>
+      </c>
+      <c r="B16" s="8">
+        <v>0.449</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0.265</v>
+      </c>
+      <c r="D16" s="11">
+        <v>0.15</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0.168</v>
+      </c>
+      <c r="F16" s="1">
+        <f t="shared" si="0"/>
+        <v>0.449</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B17" s="8">
+        <v>1.696</v>
+      </c>
+      <c r="C17" s="6">
+        <v>1.58</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0.823</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1.316</v>
+      </c>
+      <c r="F17" s="1">
+        <f t="shared" si="0"/>
+        <v>1.696</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" spans="1:6">
+      <c r="A19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="3">
+        <f>SUM(B3:B17)/15</f>
+        <v>0.277733333333333</v>
+      </c>
+      <c r="C19" s="3">
+        <f>SUM(C3:C17)/15</f>
+        <v>0.2226</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="4">
+        <f>SUM(E3:E17)/15</f>
+        <v>0.28</v>
+      </c>
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="4">
+        <f>SUM(B5:B17)/13</f>
+        <v>0.453769230769231</v>
+      </c>
+      <c r="C20" s="3">
+        <f>SUM(C5:C17)/13</f>
+        <v>0.379538461538462</v>
+      </c>
+      <c r="D20" s="3">
+        <f>SUM(D5:D17)/13</f>
+        <v>0.404076923076923</v>
+      </c>
+      <c r="E20" s="3">
+        <f>SUM(E5:E17)/13</f>
+        <v>0.444076923076923</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="F1:F2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="13" width="9.02654867256637" style="1"/>
+    <col min="1" max="1" width="9.02654867256637" style="1"/>
+    <col min="2" max="2" width="15.4778761061947" style="1" customWidth="1"/>
+    <col min="3" max="13" width="9.02654867256637" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -2247,37 +2764,37 @@
     </row>
     <row r="2" spans="1:13">
       <c r="B2" s="3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2302,7 +2819,7 @@
       <c r="G3" s="1">
         <v>-0.864</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="2">
         <v>0.422</v>
       </c>
       <c r="I3" s="1">
@@ -2338,7 +2855,7 @@
       <c r="E4" s="1">
         <v>4.243</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="2">
         <v>7.035</v>
       </c>
       <c r="G4" s="1">
@@ -2383,7 +2900,7 @@
       <c r="F5" s="1">
         <v>4.154</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="2">
         <v>4.938</v>
       </c>
       <c r="H5" s="1">
@@ -2425,7 +2942,7 @@
       <c r="F6" s="1">
         <v>-1.248</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="2">
         <v>-0.906</v>
       </c>
       <c r="H6" s="1">
@@ -2461,7 +2978,7 @@
       <c r="D7" s="1">
         <v>2.542</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="2">
         <v>3.928</v>
       </c>
       <c r="F7" s="1">
@@ -2518,7 +3035,7 @@
       <c r="I8" s="1">
         <v>-0.796</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8" s="2">
         <v>1.122</v>
       </c>
       <c r="K8" s="1">
@@ -2554,7 +3071,7 @@
       <c r="G9" s="1">
         <v>-1.562</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="2">
         <v>-0.827</v>
       </c>
       <c r="I9" s="1">
@@ -2596,7 +3113,7 @@
       <c r="G10" s="1">
         <v>0.306</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="2">
         <v>0.791</v>
       </c>
       <c r="I10" s="1">
@@ -2642,9 +3159,9 @@
         <v>-0.382</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="J11" s="5">
+        <v>34</v>
+      </c>
+      <c r="J11" s="2">
         <v>1.407</v>
       </c>
       <c r="K11" s="1">
@@ -2692,7 +3209,7 @@
       <c r="K12" s="1">
         <v>1.259</v>
       </c>
-      <c r="L12" s="5">
+      <c r="L12" s="2">
         <v>3.636</v>
       </c>
       <c r="M12" s="1">
@@ -2728,7 +3245,7 @@
       <c r="I13" s="1">
         <v>0.865</v>
       </c>
-      <c r="J13" s="5">
+      <c r="J13" s="2">
         <v>1.191</v>
       </c>
       <c r="K13" s="1">
@@ -2758,7 +3275,7 @@
       <c r="E14" s="1">
         <v>-0.816</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="2">
         <v>-0.105</v>
       </c>
       <c r="G14" s="1">
@@ -2800,7 +3317,7 @@
       <c r="E15" s="1">
         <v>0.904</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="2">
         <v>3.012</v>
       </c>
       <c r="G15" s="1">
@@ -2842,7 +3359,7 @@
       <c r="E16" s="1">
         <v>-1.541</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="2">
         <v>-0.892</v>
       </c>
       <c r="G16" s="1">
@@ -2884,7 +3401,7 @@
       <c r="E17" s="1">
         <v>1.262</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="2">
         <v>2.589</v>
       </c>
       <c r="G17" s="1">
@@ -2926,7 +3443,7 @@
       <c r="E18" s="1">
         <v>1.664</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="2">
         <v>2.48</v>
       </c>
       <c r="G18" s="1">
@@ -2986,7 +3503,7 @@
       <c r="K19" s="1">
         <v>0.028</v>
       </c>
-      <c r="L19" s="5">
+      <c r="L19" s="2">
         <v>1.264</v>
       </c>
       <c r="M19" s="1">
@@ -2998,7 +3515,7 @@
       <c r="A20" s="1">
         <v>2022</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20" s="2">
         <v>0.273</v>
       </c>
       <c r="C20" s="1">
@@ -3067,7 +3584,7 @@
       <c r="J21" s="1">
         <v>-0.032</v>
       </c>
-      <c r="K21" s="5">
+      <c r="K21" s="2">
         <v>0.535</v>
       </c>
       <c r="L21" s="1">
@@ -3100,7 +3617,7 @@
       <c r="G22" s="1">
         <v>-0.594</v>
       </c>
-      <c r="H22" s="5">
+      <c r="H22" s="2">
         <v>1.452</v>
       </c>
       <c r="I22" s="1">
@@ -3127,7 +3644,7 @@
       <c r="B23" s="1">
         <v>-0.227</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="2">
         <v>2.779</v>
       </c>
       <c r="D23" s="1">
@@ -3161,6 +3678,56 @@
         <f t="shared" si="0"/>
         <v>2.779</v>
       </c>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="3">
+        <f>SUM(B3:B23)/21</f>
+        <v>0.393904761904762</v>
+      </c>
+      <c r="C25" s="3">
+        <f t="shared" ref="C25:M25" si="1">SUM(C3:C23)/21</f>
+        <v>0.550285714285714</v>
+      </c>
+      <c r="D25" s="3">
+        <f t="shared" si="1"/>
+        <v>0.439761904761905</v>
+      </c>
+      <c r="E25" s="3">
+        <f t="shared" si="1"/>
+        <v>0.542857142857143</v>
+      </c>
+      <c r="F25" s="4">
+        <f t="shared" si="1"/>
+        <v>0.794857142857143</v>
+      </c>
+      <c r="G25" s="3">
+        <f t="shared" si="1"/>
+        <v>0.527761904761905</v>
+      </c>
+      <c r="H25" s="5">
+        <f t="shared" si="1"/>
+        <v>0.654238095238095</v>
+      </c>
+      <c r="I25" s="3">
+        <f t="shared" si="1"/>
+        <v>0.406095238095238</v>
+      </c>
+      <c r="J25" s="3">
+        <f t="shared" si="1"/>
+        <v>0.468095238095238</v>
+      </c>
+      <c r="K25" s="3">
+        <f t="shared" si="1"/>
+        <v>0.529285714285714</v>
+      </c>
+      <c r="L25" s="3">
+        <f t="shared" si="1"/>
+        <v>0.204190476190476</v>
+      </c>
+      <c r="M25" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3173,387 +3740,957 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="5.38938053097345" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.24778761061947" style="3" customWidth="1"/>
-    <col min="3" max="3" width="8.38938053097345" style="3" customWidth="1"/>
-    <col min="4" max="4" width="9.38938053097345" style="3" customWidth="1"/>
+    <col min="1" max="1" width="7.31858407079646" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.3097345132743" style="1" customWidth="1"/>
+    <col min="3" max="4" width="10.3185840707965" style="1" customWidth="1"/>
+    <col min="5" max="6" width="11.4513274336283" style="1" customWidth="1"/>
+    <col min="7" max="7" width="7.53097345132743" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="B2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="1"/>
-    </row>
-    <row r="3" spans="1:5">
+    <row r="2" spans="1:7">
+      <c r="B2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="1">
+        <v>2014</v>
+      </c>
+      <c r="B3" s="2">
+        <v>2.703</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.06</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2.019</v>
+      </c>
+      <c r="E3" s="1">
+        <v>2.468</v>
+      </c>
+      <c r="F3" s="1">
+        <v>2.513</v>
+      </c>
+      <c r="G3" s="1">
+        <f>MAX(B3:F3)</f>
+        <v>2.703</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1">
+        <v>2015</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.346</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.024</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.613</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1.122</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.183</v>
+      </c>
+      <c r="G4" s="1">
+        <f t="shared" ref="G4:G14" si="0">MAX(B4:F4)</f>
+        <v>1.122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1">
+        <v>2016</v>
+      </c>
+      <c r="B5" s="2">
+        <v>-0.322</v>
+      </c>
+      <c r="C5" s="1">
+        <v>-0.405</v>
+      </c>
+      <c r="D5" s="1">
+        <v>-0.366</v>
+      </c>
+      <c r="E5" s="1">
+        <v>-0.4</v>
+      </c>
+      <c r="F5" s="1">
+        <v>-0.38</v>
+      </c>
+      <c r="G5" s="1">
+        <f t="shared" si="0"/>
+        <v>-0.322</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1">
+        <v>2017</v>
+      </c>
+      <c r="B6" s="1">
+        <v>3.07</v>
+      </c>
+      <c r="C6" s="2">
+        <v>3.699</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.974</v>
+      </c>
+      <c r="E6" s="1">
+        <v>-0.993</v>
+      </c>
+      <c r="F6" s="1">
+        <v>3.557</v>
+      </c>
+      <c r="G6" s="1">
+        <f t="shared" si="0"/>
+        <v>3.699</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1">
+        <v>2018</v>
+      </c>
+      <c r="B7" s="1">
+        <v>-1.002</v>
+      </c>
+      <c r="C7" s="1">
+        <v>-1.008</v>
+      </c>
+      <c r="D7" s="1">
+        <v>-1.101</v>
+      </c>
+      <c r="E7" s="1">
+        <v>-1.129</v>
+      </c>
+      <c r="F7" s="2">
+        <v>-0.856</v>
+      </c>
+      <c r="G7" s="1">
+        <f t="shared" si="0"/>
+        <v>-0.856</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="1">
+        <v>2019</v>
+      </c>
+      <c r="B8" s="1">
+        <v>0.965</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.855</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.833</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1.007</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1.004</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" si="0"/>
+        <v>1.007</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="1">
+        <v>2020</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0.295</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.444</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.203</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0.68</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.285</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="0"/>
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="1">
+        <v>2021</v>
+      </c>
+      <c r="B10" s="2">
+        <v>1.21</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.402</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.775</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1.101</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0.953</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="0"/>
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="1">
+        <v>2022</v>
+      </c>
+      <c r="B11" s="1">
+        <v>-0.486</v>
+      </c>
+      <c r="C11" s="1">
+        <v>-0.653</v>
+      </c>
+      <c r="D11" s="1">
+        <v>-0.588</v>
+      </c>
+      <c r="E11" s="2">
+        <v>-0.061</v>
+      </c>
+      <c r="F11" s="1">
+        <v>-0.558</v>
+      </c>
+      <c r="G11" s="1">
+        <f t="shared" si="0"/>
+        <v>-0.061</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="1">
+        <v>2023</v>
+      </c>
+      <c r="B12" s="1">
+        <v>0.607</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0.278</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0.238</v>
+      </c>
+      <c r="E12" s="1">
+        <v>-0.305</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.668</v>
+      </c>
+      <c r="G12" s="1">
+        <f t="shared" si="0"/>
+        <v>0.668</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="1">
+        <v>2024</v>
+      </c>
+      <c r="B13" s="1">
+        <v>1.357</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1.577</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0.606</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0.433</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1.347</v>
+      </c>
+      <c r="G13" s="1">
+        <f t="shared" si="0"/>
+        <v>1.577</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B14" s="1">
+        <v>0.763</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0.436</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1.599</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0.771</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0.516</v>
+      </c>
+      <c r="G14" s="1">
+        <f t="shared" si="0"/>
+        <v>1.599</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="4">
+        <f>SUM(B3:B14)/12</f>
+        <v>0.792166666666667</v>
+      </c>
+      <c r="C16" s="3">
+        <f>SUM(C3:C14)/12</f>
+        <v>0.642416666666667</v>
+      </c>
+      <c r="D16" s="3">
+        <f>SUM(D3:D14)/12</f>
+        <v>0.48375</v>
+      </c>
+      <c r="E16" s="3">
+        <f>SUM(E3:E14)/12</f>
+        <v>0.391166666666667</v>
+      </c>
+      <c r="F16" s="3">
+        <f>SUM(F3:F14)/12</f>
+        <v>0.769333333333333</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="G1:G2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="16.0088495575221" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.24778761061947" style="5" customWidth="1"/>
+    <col min="3" max="3" width="8.53097345132743" style="5" customWidth="1"/>
+    <col min="4" max="5" width="8.38938053097345" style="5" customWidth="1"/>
+    <col min="6" max="7" width="9.38938053097345" style="5" customWidth="1"/>
+    <col min="8" max="8" width="7.53097345132743" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="B2" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2005</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="6">
         <v>-0.706</v>
       </c>
-      <c r="E3">
-        <f>MAX(B3:D3)</f>
-        <v>-0.706</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="D3" s="5">
+        <v>-0.918</v>
+      </c>
+      <c r="E3" s="4">
+        <v>-0.317</v>
+      </c>
+      <c r="H3">
+        <f>MAX(B3:G3)</f>
+        <v>-0.317</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>2006</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="6">
         <v>4.463</v>
       </c>
-      <c r="E4">
-        <f t="shared" ref="E4:E23" si="0">MAX(B4:D4)</f>
-        <v>4.463</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="D4" s="4">
+        <v>4.621</v>
+      </c>
+      <c r="E4" s="5">
+        <v>3.601</v>
+      </c>
+      <c r="H4">
+        <f t="shared" ref="H4:H23" si="0">MAX(B4:G4)</f>
+        <v>4.621</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>2007</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="6">
         <v>4.523</v>
       </c>
-      <c r="E5">
-        <f t="shared" si="0"/>
-        <v>4.523</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="D5" s="4">
+        <v>4.882</v>
+      </c>
+      <c r="E5" s="5">
+        <v>4.369</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="0"/>
+        <v>4.882</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>2008</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="6">
         <v>-1.44</v>
       </c>
-      <c r="E6">
-        <f t="shared" si="0"/>
-        <v>-1.44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="D6" s="5">
+        <v>-1.422</v>
+      </c>
+      <c r="E6" s="4">
+        <v>-1.112</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="0"/>
+        <v>-1.112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>2009</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="6">
         <v>2.911</v>
       </c>
-      <c r="E7">
-        <f t="shared" si="0"/>
-        <v>2.911</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="D7" s="5">
+        <v>2.879</v>
+      </c>
+      <c r="E7" s="4">
+        <v>3.413</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="0"/>
+        <v>3.413</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>2010</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="6">
         <v>-0.682</v>
       </c>
-      <c r="E8">
-        <f t="shared" si="0"/>
-        <v>-0.682</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="D8" s="5">
+        <v>-0.62</v>
+      </c>
+      <c r="E8" s="4">
+        <v>0.575</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="0"/>
+        <v>0.575</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>2011</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="7">
         <v>-1.36</v>
       </c>
-      <c r="E9">
+      <c r="D9" s="5">
+        <v>-1.379</v>
+      </c>
+      <c r="E9" s="5">
+        <v>-1.482</v>
+      </c>
+      <c r="H9">
         <f t="shared" si="0"/>
         <v>-1.36</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>2012</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="7">
         <v>0.215</v>
       </c>
-      <c r="E10">
+      <c r="D10" s="5">
+        <v>0.079</v>
+      </c>
+      <c r="E10" s="5">
+        <v>-0.223</v>
+      </c>
+      <c r="H10">
         <f t="shared" si="0"/>
         <v>0.215</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>2013</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="6">
         <v>-0.57</v>
       </c>
-      <c r="E11">
-        <f t="shared" si="0"/>
-        <v>-0.57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="D11" s="5">
+        <v>-0.68</v>
+      </c>
+      <c r="E11" s="4">
+        <v>0.706</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="0"/>
+        <v>0.706</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="1">
         <v>2014</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="5">
         <v>2.727</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="5">
         <v>2.634</v>
       </c>
       <c r="D12" s="4">
+        <v>3.048</v>
+      </c>
+      <c r="E12" s="5">
+        <v>1.692</v>
+      </c>
+      <c r="F12" s="5">
+        <v>1.224</v>
+      </c>
+      <c r="G12" s="6">
         <v>2.995</v>
       </c>
-      <c r="E12">
-        <f t="shared" si="0"/>
-        <v>2.995</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="H12">
+        <f t="shared" si="0"/>
+        <v>3.048</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="1">
         <v>2015</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="6">
         <v>0.573</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="5">
         <v>0.563</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="5">
+        <v>0.097</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0.941</v>
+      </c>
+      <c r="F13" s="4">
+        <v>1.554</v>
+      </c>
+      <c r="G13" s="5">
         <v>0.187</v>
       </c>
-      <c r="E13">
-        <f t="shared" si="0"/>
-        <v>0.573</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="H13">
+        <f t="shared" si="0"/>
+        <v>1.554</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="1">
         <v>2016</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="5">
         <v>-0.497</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="5">
         <v>-0.599</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="5">
+        <v>-0.47</v>
+      </c>
+      <c r="E14" s="5">
+        <v>-0.522</v>
+      </c>
+      <c r="F14" s="5">
+        <v>-0.533</v>
+      </c>
+      <c r="G14" s="7">
         <v>-0.387</v>
       </c>
-      <c r="E14">
+      <c r="H14">
         <f t="shared" si="0"/>
         <v>-0.387</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:8">
       <c r="A15" s="1">
         <v>2017</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="5">
         <v>1.587</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="5">
         <v>1.289</v>
       </c>
       <c r="D15" s="4">
+        <v>2.708</v>
+      </c>
+      <c r="E15" s="5">
+        <v>-0.178</v>
+      </c>
+      <c r="F15" s="5">
+        <v>-0.579</v>
+      </c>
+      <c r="G15" s="6">
         <v>2.59</v>
       </c>
-      <c r="E15">
-        <f t="shared" si="0"/>
-        <v>2.59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="H15">
+        <f t="shared" si="0"/>
+        <v>2.708</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="1">
         <v>2018</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="5">
         <v>-1.176</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="5">
         <v>-1.258</v>
       </c>
       <c r="D16" s="4">
+        <v>-1.107</v>
+      </c>
+      <c r="E16" s="5">
+        <v>-1.208</v>
+      </c>
+      <c r="F16" s="5">
+        <v>-1.368</v>
+      </c>
+      <c r="G16" s="6">
         <v>-1.126</v>
       </c>
-      <c r="E16">
-        <f t="shared" si="0"/>
-        <v>-1.126</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="H16">
+        <f t="shared" si="0"/>
+        <v>-1.107</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="1">
         <v>2019</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="5">
         <v>0.726</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="7">
         <v>1.099</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="6">
+        <v>1.084</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0.464</v>
+      </c>
+      <c r="F17" s="6">
+        <v>1.066</v>
+      </c>
+      <c r="G17" s="5">
         <v>1.034</v>
       </c>
-      <c r="E17">
+      <c r="H17">
         <f t="shared" si="0"/>
         <v>1.099</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:8">
       <c r="A18" s="1">
         <v>2020</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="5">
         <v>0.023</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="5">
         <v>0.217</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="5">
+        <v>0.008</v>
+      </c>
+      <c r="E18" s="5">
+        <v>-0.033</v>
+      </c>
+      <c r="F18" s="4">
+        <v>0.506</v>
+      </c>
+      <c r="G18" s="6">
         <v>0.264</v>
       </c>
-      <c r="E18">
-        <f t="shared" si="0"/>
-        <v>0.264</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="H18">
+        <f t="shared" si="0"/>
+        <v>0.506</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="1">
         <v>2021</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="6">
         <v>0.644</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="5">
         <v>0.456</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="5">
+        <v>-0.469</v>
+      </c>
+      <c r="E19" s="5">
+        <v>0.734</v>
+      </c>
+      <c r="F19" s="4">
+        <v>1.314</v>
+      </c>
+      <c r="G19" s="5">
         <v>0.36</v>
       </c>
-      <c r="E19">
-        <f t="shared" si="0"/>
-        <v>0.644</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="H19">
+        <f t="shared" si="0"/>
+        <v>1.314</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="1">
         <v>2022</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="7">
         <v>-0.421</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="5">
         <v>-0.675</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="5">
+        <v>-0.533</v>
+      </c>
+      <c r="E20" s="5">
+        <v>-0.443</v>
+      </c>
+      <c r="F20" s="5">
+        <v>-0.699</v>
+      </c>
+      <c r="G20" s="5">
         <v>-0.55</v>
       </c>
-      <c r="E20">
+      <c r="H20">
         <f t="shared" si="0"/>
         <v>-0.421</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:8">
       <c r="A21" s="1">
         <v>2023</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="6">
         <v>-0.193</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="5">
         <v>-0.296</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="5">
+        <v>-0.402</v>
+      </c>
+      <c r="E21" s="4">
+        <v>0.164</v>
+      </c>
+      <c r="F21" s="5">
+        <v>-0.474</v>
+      </c>
+      <c r="G21" s="5">
         <v>-0.523</v>
       </c>
-      <c r="E21">
-        <f t="shared" si="0"/>
-        <v>-0.193</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="H21">
+        <f t="shared" si="0"/>
+        <v>0.164</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="1">
         <v>2024</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="5">
         <v>0.492</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="5">
         <v>0.554</v>
       </c>
       <c r="D22" s="4">
+        <v>1.121</v>
+      </c>
+      <c r="E22" s="5">
+        <v>0.358</v>
+      </c>
+      <c r="F22" s="5">
+        <v>0.312</v>
+      </c>
+      <c r="G22" s="6">
         <v>0.802</v>
       </c>
-      <c r="E22">
-        <f t="shared" si="0"/>
-        <v>0.802</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="H22">
+        <f t="shared" si="0"/>
+        <v>1.121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" s="1">
         <v>2025</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23" s="5">
         <v>-0.365</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="5">
         <v>0.095</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="5">
+        <v>-0.119</v>
+      </c>
+      <c r="E23" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="F23" s="4">
+        <v>0.179</v>
+      </c>
+      <c r="G23" s="6">
         <v>0.1</v>
       </c>
-      <c r="E23">
-        <f t="shared" si="0"/>
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="H23">
+        <f t="shared" si="0"/>
+        <v>0.179</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" s="3">
+        <v>8</v>
+      </c>
+      <c r="B25" s="5">
         <f>SUM(B12:B23)/12</f>
         <v>0.343333333333333</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="5">
         <f>SUM(C12:C23)/12</f>
         <v>0.339916666666667</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="5">
         <f>SUM(D12:D23)/12</f>
+        <v>0.413833333333333</v>
+      </c>
+      <c r="E25" s="5">
+        <f>SUM(E12:E23)/12</f>
+        <v>0.171583333333333</v>
+      </c>
+      <c r="F25" s="5">
+        <f>SUM(F12:F23)/12</f>
+        <v>0.2085</v>
+      </c>
+      <c r="G25" s="7">
+        <f>SUM(G12:G23)/12</f>
         <v>0.478833333333333</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="5">
+        <f>SUM(B3:B23)/21</f>
+        <v>0.546380952380952</v>
+      </c>
+      <c r="D26" s="4">
+        <f>SUM(D3:D23)/21</f>
+        <v>0.590857142857143</v>
+      </c>
+      <c r="E26" s="5">
+        <f>SUM(E3:E23)/21</f>
+        <v>0.551857142857143</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B1:G1"/>
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="H1:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -3561,13 +4698,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="5.53097345132743" style="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5309734513274" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.24778761061947" style="1" customWidth="1"/>
     <col min="3" max="4" width="12.5132743362832" style="1" customWidth="1"/>
     <col min="5" max="5" width="13.646017699115" style="1" customWidth="1"/>
@@ -3588,22 +4725,22 @@
     </row>
     <row r="2" spans="1:8">
       <c r="B2" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="H2" s="1"/>
     </row>
@@ -4086,6 +5223,55 @@
         <f t="shared" si="0"/>
         <v>0.158</v>
       </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" s="3">
+        <f>SUM(B12:B23)/12</f>
+        <v>0.404583333333333</v>
+      </c>
+      <c r="C25" s="3">
+        <f>SUM(C12:C23)/12</f>
+        <v>0.450416666666667</v>
+      </c>
+      <c r="D25" s="3">
+        <f>SUM(D12:D23)/12</f>
+        <v>0.417666666666667</v>
+      </c>
+      <c r="E25" s="3">
+        <f>SUM(E12:E23)/12</f>
+        <v>0.24725</v>
+      </c>
+      <c r="F25" s="3">
+        <f>SUM(F12:F23)/12</f>
+        <v>0.446583333333333</v>
+      </c>
+      <c r="G25" s="4">
+        <f>SUM(G12:G23)/12</f>
+        <v>0.589666666666667</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" s="4">
+        <f>SUM(B4:B23)/20</f>
+        <v>0.71945</v>
+      </c>
+      <c r="C26" s="3">
+        <f>SUM(C4:C23)/20</f>
+        <v>0.64445</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3">
+        <f>SUM(F4:F23)/20</f>
+        <v>0.70375</v>
+      </c>
+      <c r="G26" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4096,344 +5282,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelCol="6"/>
-  <cols>
-    <col min="1" max="1" width="5.53097345132743" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.3097345132743" style="1" customWidth="1"/>
-    <col min="3" max="4" width="10.3185840707965" style="1" customWidth="1"/>
-    <col min="5" max="6" width="11.4513274336283" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7.31858407079646" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="B2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1">
-        <v>2014</v>
-      </c>
-      <c r="B3" s="2">
-        <v>2.703</v>
-      </c>
-      <c r="C3" s="1">
-        <v>2.06</v>
-      </c>
-      <c r="D3" s="1">
-        <v>2.019</v>
-      </c>
-      <c r="E3" s="1">
-        <v>2.468</v>
-      </c>
-      <c r="F3" s="1">
-        <v>2.513</v>
-      </c>
-      <c r="G3" s="1">
-        <f>MAX(B3:F3)</f>
-        <v>2.703</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1">
-        <v>2015</v>
-      </c>
-      <c r="B4" s="1">
-        <v>0.346</v>
-      </c>
-      <c r="C4" s="1">
-        <v>0.024</v>
-      </c>
-      <c r="D4" s="1">
-        <v>0.613</v>
-      </c>
-      <c r="E4" s="2">
-        <v>1.122</v>
-      </c>
-      <c r="F4" s="1">
-        <v>0.183</v>
-      </c>
-      <c r="G4" s="1">
-        <f t="shared" ref="G4:G14" si="0">MAX(B4:F4)</f>
-        <v>1.122</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="1">
-        <v>2016</v>
-      </c>
-      <c r="B5" s="2">
-        <v>-0.322</v>
-      </c>
-      <c r="C5" s="1">
-        <v>-0.405</v>
-      </c>
-      <c r="D5" s="1">
-        <v>-0.366</v>
-      </c>
-      <c r="E5" s="1">
-        <v>-0.4</v>
-      </c>
-      <c r="F5" s="1">
-        <v>-0.38</v>
-      </c>
-      <c r="G5" s="1">
-        <f t="shared" si="0"/>
-        <v>-0.322</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1">
-        <v>2017</v>
-      </c>
-      <c r="B6" s="1">
-        <v>3.07</v>
-      </c>
-      <c r="C6" s="2">
-        <v>3.699</v>
-      </c>
-      <c r="D6" s="1">
-        <v>0.974</v>
-      </c>
-      <c r="E6" s="1">
-        <v>-0.993</v>
-      </c>
-      <c r="F6" s="1">
-        <v>3.557</v>
-      </c>
-      <c r="G6" s="1">
-        <f t="shared" si="0"/>
-        <v>3.699</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="1">
-        <v>2018</v>
-      </c>
-      <c r="B7" s="1">
-        <v>-1.002</v>
-      </c>
-      <c r="C7" s="1">
-        <v>-1.008</v>
-      </c>
-      <c r="D7" s="1">
-        <v>-1.101</v>
-      </c>
-      <c r="E7" s="1">
-        <v>-1.129</v>
-      </c>
-      <c r="F7" s="2">
-        <v>-0.856</v>
-      </c>
-      <c r="G7" s="1">
-        <f t="shared" si="0"/>
-        <v>-0.856</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="1">
-        <v>2019</v>
-      </c>
-      <c r="B8" s="1">
-        <v>0.965</v>
-      </c>
-      <c r="C8" s="1">
-        <v>0.855</v>
-      </c>
-      <c r="D8" s="1">
-        <v>0.833</v>
-      </c>
-      <c r="E8" s="2">
-        <v>1.007</v>
-      </c>
-      <c r="F8" s="1">
-        <v>1.004</v>
-      </c>
-      <c r="G8" s="1">
-        <f t="shared" si="0"/>
-        <v>1.007</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="1">
-        <v>2020</v>
-      </c>
-      <c r="B9" s="1">
-        <v>0.295</v>
-      </c>
-      <c r="C9" s="1">
-        <v>0.444</v>
-      </c>
-      <c r="D9" s="1">
-        <v>0.203</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0.68</v>
-      </c>
-      <c r="F9" s="1">
-        <v>0.285</v>
-      </c>
-      <c r="G9" s="1">
-        <f t="shared" si="0"/>
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="1">
-        <v>2021</v>
-      </c>
-      <c r="B10" s="2">
-        <v>1.21</v>
-      </c>
-      <c r="C10" s="1">
-        <v>0.402</v>
-      </c>
-      <c r="D10" s="1">
-        <v>0.775</v>
-      </c>
-      <c r="E10" s="1">
-        <v>1.101</v>
-      </c>
-      <c r="F10" s="1">
-        <v>0.953</v>
-      </c>
-      <c r="G10" s="1">
-        <f t="shared" si="0"/>
-        <v>1.21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="1">
-        <v>2022</v>
-      </c>
-      <c r="B11" s="1">
-        <v>-0.486</v>
-      </c>
-      <c r="C11" s="1">
-        <v>-0.653</v>
-      </c>
-      <c r="D11" s="1">
-        <v>-0.588</v>
-      </c>
-      <c r="E11" s="2">
-        <v>-0.061</v>
-      </c>
-      <c r="F11" s="1">
-        <v>-0.558</v>
-      </c>
-      <c r="G11" s="1">
-        <f t="shared" si="0"/>
-        <v>-0.061</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="1">
-        <v>2023</v>
-      </c>
-      <c r="B12" s="1">
-        <v>0.607</v>
-      </c>
-      <c r="C12" s="1">
-        <v>0.278</v>
-      </c>
-      <c r="D12" s="1">
-        <v>0.238</v>
-      </c>
-      <c r="E12" s="1">
-        <v>-0.305</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0.668</v>
-      </c>
-      <c r="G12" s="1">
-        <f t="shared" si="0"/>
-        <v>0.668</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="1">
-        <v>2024</v>
-      </c>
-      <c r="B13" s="1">
-        <v>1.357</v>
-      </c>
-      <c r="C13" s="2">
-        <v>1.577</v>
-      </c>
-      <c r="D13" s="1">
-        <v>0.606</v>
-      </c>
-      <c r="E13" s="1">
-        <v>0.433</v>
-      </c>
-      <c r="F13" s="1">
-        <v>1.347</v>
-      </c>
-      <c r="G13" s="1">
-        <f t="shared" si="0"/>
-        <v>1.577</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="1">
-        <v>2025</v>
-      </c>
-      <c r="B14" s="1">
-        <v>0.763</v>
-      </c>
-      <c r="C14" s="1">
-        <v>0.436</v>
-      </c>
-      <c r="D14" s="2">
-        <v>1.599</v>
-      </c>
-      <c r="E14" s="1">
-        <v>0.771</v>
-      </c>
-      <c r="F14" s="1">
-        <v>0.516</v>
-      </c>
-      <c r="G14" s="1">
-        <f t="shared" si="0"/>
-        <v>1.599</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="G1:G2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
 </file>